--- a/data/numeric/input/old_data_36/附件2_2023年统计的相关数据.xlsx
+++ b/data/numeric/input/old_data_36/附件2_2023年统计的相关数据.xlsx
@@ -1,28 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sunyixuan/Desktop/wps_1.1_files_脱敏后/DLG_66/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0205/ai办公标注/input/old_data_36/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C37DDBD-2EF1-6C4D-988F-F002E995063C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED27FAE-6E58-AC4B-9188-D61483C3EB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1060" yWindow="760" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="108">
   <si>
     <t>序号</t>
   </si>
@@ -51,6 +67,10 @@
     <t>1</t>
   </si>
   <si>
+    <t>作物A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>平旱地</t>
   </si>
   <si>
@@ -300,9 +320,6 @@
     <t>31</t>
   </si>
   <si>
-    <t>袁畅</t>
-  </si>
-  <si>
     <t>山坡地</t>
   </si>
   <si>
@@ -346,14 +363,6 @@
   </si>
   <si>
     <t>40</t>
-  </si>
-  <si>
-    <t>孙*梅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朱*兰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -701,7 +710,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
@@ -737,802 +746,802 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="D32" t="s">
         <v>93</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1540,25 +1549,25 @@
         <v>94</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
         <v>93</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1566,25 +1575,25 @@
         <v>95</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D34" t="s">
         <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1592,25 +1601,25 @@
         <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
         <v>93</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F35" t="s">
         <v>97</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1618,25 +1627,25 @@
         <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D36" t="s">
         <v>93</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F36" t="s">
         <v>99</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1644,25 +1653,25 @@
         <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
         <v>93</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F37" t="s">
         <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1670,25 +1679,25 @@
         <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
         <v>93</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F38" t="s">
         <v>103</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1696,25 +1705,25 @@
         <v>104</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D39" t="s">
         <v>93</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1722,25 +1731,25 @@
         <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D40" t="s">
         <v>93</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F40" t="s">
         <v>106</v>
       </c>
       <c r="G40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1748,25 +1757,25 @@
         <v>107</v>
       </c>
       <c r="B41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D41" t="s">
         <v>93</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1778,7 +1787,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1788,7 +1797,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1796,6 +1805,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -1943,29 +1967,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D138874B-5B13-4A74-9870-FF0988365DC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05EF478D-CCEF-4409-BC59-D0182A7DFB56}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{535CB376-34EF-41B5-969B-533DB3C8EF63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6119FA8-88D7-43D4-8A12-4A45D8F0CA9E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDAE26C4-7A94-4B43-AB69-37AF583DEEC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1587ECF5-5318-4C5A-9C93-C93836BB7FD0}"/>
 </file>